--- a/Data/evenements.xlsx
+++ b/Data/evenements.xlsx
@@ -59,6 +59,66 @@
   </x:si>
   <x:si>
     <x:t>2026-03-30 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Entrainement</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-31 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-03-31 10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Terrain de l'école</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-07 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-07 10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-14 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-14 10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-21 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-21 10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-28 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-28 10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-05 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-05 10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-12 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-12 10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-19 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-19 10:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-26 09:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-26 10:00</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -490,6 +550,240 @@
         <x:v>12</x:v>
       </x:c>
     </x:row>
+    <x:row r="4" spans="1:8">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="A6" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8">
+      <x:c r="A7" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8">
+      <x:c r="A8" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8">
+      <x:c r="A9" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:8">
+      <x:c r="A10" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:8">
+      <x:c r="A11" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:8">
+      <x:c r="A12" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/evenements.xlsx
+++ b/Data/evenements.xlsx
@@ -38,87 +38,6 @@
   </x:si>
   <x:si>
     <x:t>Notes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pratique</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-03-30 10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-03-30 11:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Terrain</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>pratique</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-03-30 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Entrainement</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-03-31 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-03-31 10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Terrain de l'école</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-07 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-07 10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-14 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-14 10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-21 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-21 10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-28 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-28 10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-05 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-05 10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-12 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-12 10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-19 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-19 10:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-26 09:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-26 10:00</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -498,292 +417,6 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:8">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8">
-      <x:c r="A5" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8">
-      <x:c r="A6" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8">
-      <x:c r="A7" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8">
-      <x:c r="A8" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8">
-      <x:c r="A9" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8">
-      <x:c r="A10" s="0">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:8">
-      <x:c r="A11" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B11" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:8">
-      <x:c r="A12" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/evenements.xlsx
+++ b/Data/evenements.xlsx
@@ -38,6 +38,84 @@
   </x:si>
   <x:si>
     <x:t>Notes</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pratique</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-13 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-13 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-20 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-20 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-27 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-04-27 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-04 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-04 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-11 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-11 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-18 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-18 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-25 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-05-25 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-01 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-01 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-08 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-15 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-22 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-22 16:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-29 14:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2026-06-29 16:00</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -417,6 +495,318 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
+    <x:row r="2" spans="1:8">
+      <x:c r="A2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B2" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:8">
+      <x:c r="A3" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B3" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:8">
+      <x:c r="A4" s="0">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B4" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D4" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E4" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:8">
+      <x:c r="A5" s="0">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B5" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D5" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="F5" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:8">
+      <x:c r="A6" s="0">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B6" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D6" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="F6" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:8">
+      <x:c r="A7" s="0">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B7" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C7" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D7" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E7" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F7" s="0" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:8">
+      <x:c r="A8" s="0">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B8" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E8" s="0" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="F8" s="0" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:8">
+      <x:c r="A9" s="0">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B9" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C9" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:8">
+      <x:c r="A10" s="0">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="B10" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E10" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F10" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:8">
+      <x:c r="A11" s="0">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="B11" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D11" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E11" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="F11" s="0" t="s">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:8">
+      <x:c r="A12" s="0">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B12" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C12" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D12" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E12" s="0" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F12" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:8">
+      <x:c r="A13" s="0">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B13" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C13" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D13" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E13" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="F13" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>11</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>

--- a/Data/evenements.xlsx
+++ b/Data/evenements.xlsx
@@ -38,84 +38,6 @@
   </x:si>
   <x:si>
     <x:t>Notes</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pratique</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-13 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-13 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-20 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-20 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-27 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-04-27 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-04 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-04 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-11 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-11 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-18 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-18 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-25 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-05-25 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-01 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-01 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-08 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-08 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-15 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-15 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-22 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-22 16:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-29 14:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2026-06-29 16:00</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -495,318 +417,6 @@
         <x:v>7</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:8">
-      <x:c r="A2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="B2" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E2" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:8">
-      <x:c r="A3" s="0">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="B3" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:8">
-      <x:c r="A4" s="0">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="B4" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E4" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F4" s="0" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H4" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:8">
-      <x:c r="A5" s="0">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="B5" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D5" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E5" s="0" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="F5" s="0" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="G5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H5" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:8">
-      <x:c r="A6" s="0">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="B6" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D6" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="F6" s="0" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="G6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H6" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:8">
-      <x:c r="A7" s="0">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B7" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E7" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="G7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H7" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:8">
-      <x:c r="A8" s="0">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="B8" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E8" s="0" t="s">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="F8" s="0" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="G8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H8" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:8">
-      <x:c r="A9" s="0">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="B9" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="G9" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H9" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:8">
-      <x:c r="A10" s="0">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B10" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E10" s="0" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="F10" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G10" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H10" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:8">
-      <x:c r="A11" s="0">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B11" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D11" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E11" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="F11" s="0" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G11" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H11" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:8">
-      <x:c r="A12" s="0">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B12" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D12" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E12" s="0" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F12" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="G12" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H12" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:8">
-      <x:c r="A13" s="0">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B13" s="0">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C13" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D13" s="0" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E13" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="F13" s="0" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="G13" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="H13" s="0" t="s">
-        <x:v>11</x:v>
-      </x:c>
-    </x:row>
   </x:sheetData>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
